--- a/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>ZIVO</t>
   </si>
@@ -656,140 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -880,8 +883,11 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -891,8 +897,8 @@
       <c r="E9" s="3">
         <v>0</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
+      <c r="F9" s="3">
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>4</v>
@@ -972,8 +978,11 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -983,8 +992,8 @@
       <c r="E10" s="3">
         <v>0</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
+      <c r="F10" s="3">
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>4</v>
@@ -1064,8 +1073,11 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,100 +1110,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
         <v>200</v>
-      </c>
-      <c r="E12" s="3">
-        <v>400</v>
       </c>
       <c r="F12" s="3">
         <v>400</v>
       </c>
       <c r="G12" s="3">
+        <v>400</v>
+      </c>
+      <c r="H12" s="3">
         <v>500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1600</v>
-      </c>
-      <c r="S12" s="3">
-        <v>500</v>
       </c>
       <c r="T12" s="3">
         <v>500</v>
       </c>
       <c r="U12" s="3">
+        <v>500</v>
+      </c>
+      <c r="V12" s="3">
         <v>900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>400</v>
-      </c>
-      <c r="W12" s="3">
-        <v>600</v>
       </c>
       <c r="X12" s="3">
         <v>600</v>
       </c>
       <c r="Y12" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z12" s="3">
         <v>800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,13 +1298,16 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1296,27 +1315,27 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1332,8 +1351,8 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1366,16 +1385,19 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>400</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,100 +1522,104 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="3">
         <v>1600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,91 +1627,94 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1747,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1727,7 +1760,7 @@
         <v>-200</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
@@ -1775,40 +1808,43 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>-400</v>
       </c>
       <c r="X20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-300</v>
       </c>
       <c r="AE20" s="3">
         <v>-300</v>
       </c>
       <c r="AF20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1816,91 +1852,94 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>-2000</v>
+        <v>-1800</v>
       </c>
       <c r="F21" s="3">
         <v>-2000</v>
       </c>
       <c r="G21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H21" s="3">
         <v>-2600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>-900</v>
       </c>
       <c r="AF21" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1932,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
@@ -1950,141 +1989,147 @@
         <v>100</v>
       </c>
       <c r="S22" s="3">
+        <v>100</v>
+      </c>
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>500</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>400</v>
       </c>
       <c r="AD22" s="3">
         <v>400</v>
       </c>
       <c r="AE22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF22" s="3">
         <v>300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2500</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-3100</v>
       </c>
       <c r="W23" s="3">
         <v>-3100</v>
       </c>
       <c r="X23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2220,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2500</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-3100</v>
       </c>
       <c r="W26" s="3">
         <v>-3100</v>
       </c>
       <c r="X26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2500</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-3100</v>
       </c>
       <c r="W27" s="3">
         <v>-3100</v>
       </c>
       <c r="X27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2885,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2831,7 +2900,7 @@
         <v>200</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
@@ -2879,132 +2948,138 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>400</v>
       </c>
       <c r="X32" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>300</v>
       </c>
       <c r="AE32" s="3">
         <v>300</v>
       </c>
       <c r="AF32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2500</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-3100</v>
       </c>
       <c r="W33" s="3">
         <v>-3100</v>
       </c>
       <c r="X33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2500</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-3100</v>
       </c>
       <c r="W35" s="3">
         <v>-3100</v>
       </c>
       <c r="X35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,46 +3437,47 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1500</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>200</v>
-      </c>
-      <c r="O41" s="3">
-        <v>100</v>
       </c>
       <c r="P41" s="3">
         <v>100</v>
@@ -3400,14 +3486,14 @@
         <v>100</v>
       </c>
       <c r="R41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3">
         <v>300</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
         <v>0</v>
       </c>
@@ -3415,37 +3501,40 @@
         <v>0</v>
       </c>
       <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1200</v>
       </c>
-      <c r="AC41" s="3">
-        <v>0</v>
-      </c>
       <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="3">
         <v>1000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,16 +3625,19 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
         <v>0</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>4</v>
@@ -3562,8 +3654,8 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3580,14 +3672,14 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>4</v>
@@ -3604,8 +3696,8 @@
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -3628,8 +3720,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,49 +3815,52 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>500</v>
       </c>
       <c r="F45" s="3">
+        <v>500</v>
+      </c>
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>100</v>
       </c>
       <c r="L45" s="3">
         <v>100</v>
       </c>
       <c r="M45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
       </c>
       <c r="O45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
@@ -3771,10 +3869,10 @@
         <v>100</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3">
         <v>100</v>
@@ -3783,10 +3881,10 @@
         <v>100</v>
       </c>
       <c r="W45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>100</v>
@@ -3795,14 +3893,14 @@
         <v>100</v>
       </c>
       <c r="AA45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
-      </c>
       <c r="AD45" s="3">
         <v>0</v>
       </c>
@@ -3812,61 +3910,64 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="3">
         <v>1900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>100</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>200</v>
       </c>
       <c r="R46" s="3">
         <v>200</v>
       </c>
       <c r="S46" s="3">
+        <v>200</v>
+      </c>
+      <c r="T46" s="3">
         <v>400</v>
-      </c>
-      <c r="T46" s="3">
-        <v>100</v>
       </c>
       <c r="U46" s="3">
         <v>100</v>
@@ -3875,37 +3976,40 @@
         <v>100</v>
       </c>
       <c r="W46" s="3">
+        <v>100</v>
+      </c>
+      <c r="X46" s="3">
         <v>400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3945,8 +4049,8 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
+      <c r="P47" s="3">
+        <v>0</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>4</v>
@@ -3963,8 +4067,8 @@
       <c r="U47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3996,8 +4100,11 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4008,7 +4115,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G48" s="3">
         <v>200</v>
@@ -4023,7 +4130,7 @@
         <v>200</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -4088,8 +4195,11 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4290,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4480,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4396,15 +4515,15 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4420,8 +4539,8 @@
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -4432,32 +4551,35 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA52" s="3">
         <v>2600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3900</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>100</v>
       </c>
       <c r="AC52" s="3">
         <v>100</v>
       </c>
       <c r="AD52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE52" s="3">
         <v>200</v>
       </c>
       <c r="AF52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,61 +4670,64 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>100</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>200</v>
       </c>
       <c r="R54" s="3">
         <v>200</v>
       </c>
       <c r="S54" s="3">
+        <v>200</v>
+      </c>
+      <c r="T54" s="3">
         <v>400</v>
-      </c>
-      <c r="T54" s="3">
-        <v>100</v>
       </c>
       <c r="U54" s="3">
         <v>100</v>
@@ -4611,37 +4736,40 @@
         <v>100</v>
       </c>
       <c r="W54" s="3">
+        <v>100</v>
+      </c>
+      <c r="X54" s="3">
         <v>400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>700</v>
       </c>
       <c r="AF54" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,203 +4837,210 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>700</v>
       </c>
       <c r="L57" s="3">
         <v>700</v>
       </c>
       <c r="M57" s="3">
+        <v>700</v>
+      </c>
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>800</v>
-      </c>
-      <c r="W57" s="3">
-        <v>400</v>
       </c>
       <c r="X57" s="3">
         <v>400</v>
       </c>
       <c r="Y57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z57" s="3">
         <v>500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>600</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>800</v>
       </c>
       <c r="AD57" s="3">
         <v>800</v>
       </c>
       <c r="AE57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF57" s="3">
         <v>700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
         <v>1400</v>
       </c>
       <c r="F58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G58" s="3">
         <v>800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
-      </c>
-      <c r="K58" s="3">
-        <v>200</v>
       </c>
       <c r="L58" s="3">
         <v>200</v>
       </c>
       <c r="M58" s="3">
+        <v>200</v>
+      </c>
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5300</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>5200</v>
       </c>
       <c r="R58" s="3">
         <v>5200</v>
       </c>
       <c r="S58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="T58" s="3">
         <v>5300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>7500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>19700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>18600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>18300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>16400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>17000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="E59" s="3">
         <v>1200</v>
       </c>
       <c r="F59" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="G59" s="3">
         <v>1300</v>
@@ -4913,171 +5049,177 @@
         <v>1300</v>
       </c>
       <c r="I59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J59" s="3">
         <v>1700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" s="3">
         <v>3200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>24800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>22700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>19600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>18800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>11200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5109,7 +5251,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>100</v>
@@ -5124,7 +5266,7 @@
         <v>100</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -5148,28 +5290,31 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>16500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>12100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>14100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5177,7 +5322,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
@@ -5189,14 +5334,14 @@
         <v>100</v>
       </c>
       <c r="I62" s="3">
+        <v>100</v>
+      </c>
+      <c r="J62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5209,14 +5354,14 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
@@ -5260,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="3">
         <v>3200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>24800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>22700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>21900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>19600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-123600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-121700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-119800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-117800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-115800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-113200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-112300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-110300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-108200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-104700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-103100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-101300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-99100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-97200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-93700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-92500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-90000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-85800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-84000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-81500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-78400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-75400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-71200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-67700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-63800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-59900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-57100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-55600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-53800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-3100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1700</v>
       </c>
-      <c r="G76" s="3">
-        <v>0</v>
-      </c>
       <c r="H76" s="3">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3">
         <v>1500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-11400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-11300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-10000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-9100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-8300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-10900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-11200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-24700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-22300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-21600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-18800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-19600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-16300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-16600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-15300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-13600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2500</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-3100</v>
       </c>
       <c r="W81" s="3">
         <v>-3100</v>
       </c>
       <c r="X81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7095,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7575,8 +7795,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +7985,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7851,8 +8080,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8495,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E100" s="3">
         <v>3400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-200</v>
       </c>
       <c r="I100" s="3">
         <v>-200</v>
       </c>
       <c r="J100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>1700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>12700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>500</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>400</v>
       </c>
       <c r="R100" s="3">
         <v>400</v>
       </c>
       <c r="S100" s="3">
+        <v>400</v>
+      </c>
+      <c r="T100" s="3">
         <v>1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8685,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-1600</v>
       </c>
       <c r="G102" s="3">
         <v>-1600</v>
       </c>
       <c r="H102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>10700</v>
-      </c>
-      <c r="N102" s="3">
-        <v>100</v>
       </c>
       <c r="O102" s="3">
         <v>100</v>
       </c>
       <c r="P102" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>300</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
   <si>
     <t>ZIVO</t>
   </si>
@@ -656,143 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -886,8 +890,11 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -900,8 +907,8 @@
       <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>4</v>
@@ -981,8 +988,11 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -995,8 +1005,8 @@
       <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
+      <c r="G10" s="3">
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>4</v>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1120,94 +1134,97 @@
         <v>300</v>
       </c>
       <c r="E12" s="3">
+        <v>300</v>
+      </c>
+      <c r="F12" s="3">
         <v>200</v>
-      </c>
-      <c r="F12" s="3">
-        <v>400</v>
       </c>
       <c r="G12" s="3">
         <v>400</v>
       </c>
       <c r="H12" s="3">
+        <v>400</v>
+      </c>
+      <c r="I12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1600</v>
-      </c>
-      <c r="T12" s="3">
-        <v>500</v>
       </c>
       <c r="U12" s="3">
         <v>500</v>
       </c>
       <c r="V12" s="3">
+        <v>500</v>
+      </c>
+      <c r="W12" s="3">
         <v>900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>400</v>
-      </c>
-      <c r="X12" s="3">
-        <v>600</v>
       </c>
       <c r="Y12" s="3">
         <v>600</v>
       </c>
       <c r="Z12" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA12" s="3">
         <v>800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,13 +1318,16 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1318,27 +1338,27 @@
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1354,8 +1374,8 @@
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1388,16 +1408,19 @@
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>400</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,103 +1549,107 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>4</v>
+      <c r="D17" s="3">
+        <v>1300</v>
       </c>
       <c r="E17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F17" s="3">
         <v>1600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1627,94 +1657,97 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,8 +1781,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1757,13 +1791,13 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>-200</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1811,40 +1845,43 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>-400</v>
       </c>
       <c r="Y20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-300</v>
       </c>
       <c r="AF20" s="3">
         <v>-300</v>
       </c>
       <c r="AG20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1852,94 +1889,97 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-2000</v>
       </c>
       <c r="G21" s="3">
         <v>-2000</v>
       </c>
       <c r="H21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-2600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>-900</v>
       </c>
       <c r="AG21" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1947,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1974,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
@@ -1992,144 +2032,150 @@
         <v>100</v>
       </c>
       <c r="T22" s="3">
+        <v>100</v>
+      </c>
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>3100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>500</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>400</v>
       </c>
       <c r="AE22" s="3">
         <v>400</v>
       </c>
       <c r="AF22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG22" s="3">
         <v>300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>-1300</v>
       </c>
       <c r="E23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-3100</v>
       </c>
       <c r="X23" s="3">
         <v>-3100</v>
       </c>
       <c r="Y23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2223,8 +2269,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-1300</v>
       </c>
       <c r="E26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2500</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-3100</v>
       </c>
       <c r="X26" s="3">
         <v>-3100</v>
       </c>
       <c r="Y26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-1300</v>
       </c>
       <c r="E27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2500</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-3100</v>
       </c>
       <c r="X27" s="3">
         <v>-3100</v>
       </c>
       <c r="Y27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,8 +2955,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2897,13 +2967,13 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>200</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -2951,135 +3021,141 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>400</v>
       </c>
       <c r="Y32" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z32" s="3">
         <v>300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>100</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>300</v>
       </c>
       <c r="AF32" s="3">
         <v>300</v>
       </c>
       <c r="AG32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-1300</v>
       </c>
       <c r="E33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2500</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-3100</v>
       </c>
       <c r="X33" s="3">
         <v>-3100</v>
       </c>
       <c r="Y33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-1300</v>
       </c>
       <c r="E35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2500</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-3100</v>
       </c>
       <c r="X35" s="3">
         <v>-3100</v>
       </c>
       <c r="Y35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,49 +3524,50 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1500</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
       <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>200</v>
-      </c>
-      <c r="P41" s="3">
-        <v>100</v>
       </c>
       <c r="Q41" s="3">
         <v>100</v>
@@ -3489,14 +3576,14 @@
         <v>100</v>
       </c>
       <c r="S41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
         <v>300</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
       <c r="V41" s="3">
         <v>0</v>
       </c>
@@ -3504,37 +3591,40 @@
         <v>0</v>
       </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
         <v>400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1200</v>
       </c>
-      <c r="AD41" s="3">
-        <v>0</v>
-      </c>
       <c r="AE41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="3">
         <v>1000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,8 +3718,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3639,8 +3732,8 @@
       <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
+      <c r="F43" s="3">
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
@@ -3657,8 +3750,8 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3675,14 +3768,14 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>4</v>
@@ -3699,8 +3792,8 @@
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -3723,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,52 +3914,55 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
         <v>100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>500</v>
       </c>
       <c r="F45" s="3">
         <v>500</v>
       </c>
       <c r="G45" s="3">
+        <v>500</v>
+      </c>
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>100</v>
       </c>
       <c r="M45" s="3">
         <v>100</v>
       </c>
       <c r="N45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O45" s="3">
         <v>200</v>
       </c>
       <c r="P45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R45" s="3">
         <v>100</v>
@@ -3872,10 +3971,10 @@
         <v>100</v>
       </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3">
         <v>100</v>
@@ -3884,10 +3983,10 @@
         <v>100</v>
       </c>
       <c r="X45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3">
         <v>100</v>
@@ -3896,14 +3995,14 @@
         <v>100</v>
       </c>
       <c r="AB45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3">
         <v>100</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
       <c r="AE45" s="3">
         <v>0</v>
       </c>
@@ -3913,64 +4012,67 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>4</v>
+      <c r="D46" s="3">
+        <v>700</v>
       </c>
       <c r="E46" s="3">
+        <v>400</v>
+      </c>
+      <c r="F46" s="3">
         <v>1900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>100</v>
-      </c>
-      <c r="R46" s="3">
-        <v>200</v>
       </c>
       <c r="S46" s="3">
         <v>200</v>
       </c>
       <c r="T46" s="3">
+        <v>200</v>
+      </c>
+      <c r="U46" s="3">
         <v>400</v>
-      </c>
-      <c r="U46" s="3">
-        <v>100</v>
       </c>
       <c r="V46" s="3">
         <v>100</v>
@@ -3979,37 +4081,40 @@
         <v>100</v>
       </c>
       <c r="X46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y46" s="3">
         <v>400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4052,8 +4157,8 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
+      <c r="Q47" s="3">
+        <v>0</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>4</v>
@@ -4070,8 +4175,8 @@
       <c r="V47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -4103,8 +4208,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4118,7 +4226,7 @@
         <v>100</v>
       </c>
       <c r="G48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H48" s="3">
         <v>200</v>
@@ -4133,7 +4241,7 @@
         <v>200</v>
       </c>
       <c r="L48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4198,8 +4306,11 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4518,15 +4638,15 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4542,8 +4662,8 @@
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -4554,32 +4674,35 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB52" s="3">
         <v>2600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3900</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>100</v>
       </c>
       <c r="AD52" s="3">
         <v>100</v>
       </c>
       <c r="AE52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF52" s="3">
         <v>200</v>
       </c>
       <c r="AG52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,64 +4796,67 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>800</v>
+      </c>
+      <c r="E54" s="3">
         <v>600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>100</v>
-      </c>
-      <c r="R54" s="3">
-        <v>200</v>
       </c>
       <c r="S54" s="3">
         <v>200</v>
       </c>
       <c r="T54" s="3">
+        <v>200</v>
+      </c>
+      <c r="U54" s="3">
         <v>400</v>
-      </c>
-      <c r="U54" s="3">
-        <v>100</v>
       </c>
       <c r="V54" s="3">
         <v>100</v>
@@ -4739,37 +4865,40 @@
         <v>100</v>
       </c>
       <c r="X54" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y54" s="3">
         <v>400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1200</v>
-      </c>
-      <c r="AF54" s="3">
-        <v>700</v>
       </c>
       <c r="AG54" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,212 +4968,219 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>700</v>
       </c>
       <c r="M57" s="3">
         <v>700</v>
       </c>
       <c r="N57" s="3">
+        <v>700</v>
+      </c>
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>800</v>
-      </c>
-      <c r="X57" s="3">
-        <v>400</v>
       </c>
       <c r="Y57" s="3">
         <v>400</v>
       </c>
       <c r="Z57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>600</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>800</v>
       </c>
       <c r="AE57" s="3">
         <v>800</v>
       </c>
       <c r="AF57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG57" s="3">
         <v>700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
         <v>200</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1400</v>
       </c>
       <c r="F58" s="3">
         <v>1400</v>
       </c>
       <c r="G58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>800</v>
-      </c>
-      <c r="L58" s="3">
-        <v>200</v>
       </c>
       <c r="M58" s="3">
         <v>200</v>
       </c>
       <c r="N58" s="3">
+        <v>200</v>
+      </c>
+      <c r="O58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5300</v>
-      </c>
-      <c r="R58" s="3">
-        <v>5200</v>
       </c>
       <c r="S58" s="3">
         <v>5200</v>
       </c>
       <c r="T58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="U58" s="3">
         <v>5300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>19700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>18600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>18300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>16400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>17000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1400</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1200</v>
       </c>
       <c r="F59" s="3">
         <v>1200</v>
       </c>
       <c r="G59" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="H59" s="3">
         <v>1300</v>
@@ -5052,174 +5189,180 @@
         <v>1300</v>
       </c>
       <c r="J59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K59" s="3">
         <v>1700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4</v>
+      <c r="D60" s="3">
+        <v>3100</v>
       </c>
       <c r="E60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F60" s="3">
         <v>3200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>24800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>22700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>21900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>18800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>11200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5254,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>100</v>
@@ -5269,7 +5412,7 @@
         <v>100</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -5293,39 +5436,42 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>16500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>12100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>14200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>14100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
         <v>100</v>
@@ -5337,14 +5483,14 @@
         <v>100</v>
       </c>
       <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5357,14 +5503,14 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>4</v>
+      <c r="D66" s="3">
+        <v>3100</v>
       </c>
       <c r="E66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F66" s="3">
         <v>3200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>24800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>22700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>21900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>22300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>14400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-124900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-123600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-121700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-119800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-117800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-115800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-113200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-112300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-110300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-108200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-104700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-103100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-101300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-99100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-97200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-93700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-92500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-90000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-85800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-84000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-81500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-78400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-75400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-71200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-67700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-63800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-59900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-57100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-55600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-53800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-3100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1700</v>
       </c>
-      <c r="H76" s="3">
-        <v>0</v>
-      </c>
       <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
         <v>1500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-11400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-11100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-10000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-9100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-8300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-10900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-11200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-24700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-22300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-21600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-18800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-19600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-16300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-15300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-13600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-1300</v>
       </c>
       <c r="E81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2500</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-3100</v>
       </c>
       <c r="X81" s="3">
         <v>-3100</v>
       </c>
       <c r="Y81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7798,8 +8019,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,8 +8215,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8083,8 +8313,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,103 +8741,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-200</v>
       </c>
       <c r="J100" s="3">
         <v>-200</v>
       </c>
       <c r="K100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>1700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>12700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>500</v>
-      </c>
-      <c r="R100" s="3">
-        <v>400</v>
       </c>
       <c r="S100" s="3">
         <v>400</v>
       </c>
       <c r="T100" s="3">
+        <v>400</v>
+      </c>
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-1600</v>
       </c>
       <c r="H102" s="3">
         <v>-1600</v>
       </c>
       <c r="I102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>10700</v>
-      </c>
-      <c r="O102" s="3">
-        <v>100</v>
       </c>
       <c r="P102" s="3">
         <v>100</v>
       </c>
       <c r="Q102" s="3">
+        <v>100</v>
+      </c>
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>300</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
         <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>ZIVO</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -893,13 +897,16 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -910,8 +917,8 @@
       <c r="G9" s="3">
         <v>0</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
+      <c r="H9" s="3">
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>4</v>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1008,8 +1018,8 @@
       <c r="G10" s="3">
         <v>0</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
+      <c r="H10" s="3">
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>4</v>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>300</v>
+        <v>2300</v>
       </c>
       <c r="E12" s="3">
         <v>300</v>
       </c>
       <c r="F12" s="3">
+        <v>300</v>
+      </c>
+      <c r="G12" s="3">
         <v>200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>400</v>
       </c>
       <c r="H12" s="3">
         <v>400</v>
       </c>
       <c r="I12" s="3">
+        <v>400</v>
+      </c>
+      <c r="J12" s="3">
         <v>500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1600</v>
-      </c>
-      <c r="U12" s="3">
-        <v>500</v>
       </c>
       <c r="V12" s="3">
         <v>500</v>
       </c>
       <c r="W12" s="3">
+        <v>500</v>
+      </c>
+      <c r="X12" s="3">
         <v>900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>400</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>600</v>
       </c>
       <c r="Z12" s="3">
         <v>600</v>
       </c>
       <c r="AA12" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB12" s="3">
         <v>800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1341,27 +1361,27 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1377,8 +1397,8 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1411,16 +1431,19 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>400</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,106 +1576,110 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1657,97 +1687,100 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1791,16 +1825,16 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-200</v>
       </c>
       <c r="G20" s="3">
         <v>-200</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1848,40 +1882,43 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>-400</v>
       </c>
       <c r="Z20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-300</v>
       </c>
       <c r="AG20" s="3">
         <v>-300</v>
       </c>
       <c r="AH20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1889,97 +1926,100 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1800</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-2000</v>
       </c>
       <c r="H21" s="3">
         <v>-2000</v>
       </c>
       <c r="I21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J21" s="3">
         <v>-2600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AG21" s="3">
-        <v>-900</v>
       </c>
       <c r="AH21" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1987,11 +2027,11 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
@@ -2017,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
@@ -2035,147 +2075,153 @@
         <v>100</v>
       </c>
       <c r="U22" s="3">
+        <v>100</v>
+      </c>
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>500</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>400</v>
       </c>
       <c r="AF22" s="3">
         <v>400</v>
       </c>
       <c r="AG22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH22" s="3">
         <v>300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-3100</v>
       </c>
       <c r="Y23" s="3">
         <v>-3100</v>
       </c>
       <c r="Z23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-3100</v>
       </c>
       <c r="Y26" s="3">
         <v>-3100</v>
       </c>
       <c r="Z26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2500</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-3100</v>
       </c>
       <c r="Y27" s="3">
         <v>-3100</v>
       </c>
       <c r="Z27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2967,16 +3037,16 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>200</v>
       </c>
       <c r="G32" s="3">
         <v>200</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -3024,138 +3094,144 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>400</v>
       </c>
       <c r="Z32" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA32" s="3">
         <v>300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>100</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>300</v>
       </c>
       <c r="AG32" s="3">
         <v>300</v>
       </c>
       <c r="AH32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-3100</v>
       </c>
       <c r="Y33" s="3">
         <v>-3100</v>
       </c>
       <c r="Z33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-3100</v>
       </c>
       <c r="Y35" s="3">
         <v>-3100</v>
       </c>
       <c r="Z35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,52 +3611,53 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1500</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>200</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>100</v>
       </c>
       <c r="R41" s="3">
         <v>100</v>
@@ -3579,14 +3666,14 @@
         <v>100</v>
       </c>
       <c r="T41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
         <v>300</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
       <c r="W41" s="3">
         <v>0</v>
       </c>
@@ -3594,37 +3681,40 @@
         <v>0</v>
       </c>
       <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1200</v>
       </c>
-      <c r="AE41" s="3">
-        <v>0</v>
-      </c>
       <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3">
         <v>1000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,8 +3811,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3735,8 +3828,8 @@
       <c r="F43" s="3">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
@@ -3753,8 +3846,8 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3771,14 +3864,14 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>4</v>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>4</v>
@@ -3795,8 +3888,8 @@
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,55 +4013,58 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>500</v>
       </c>
       <c r="G45" s="3">
         <v>500</v>
       </c>
       <c r="H45" s="3">
+        <v>500</v>
+      </c>
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>100</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
       </c>
       <c r="O45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P45" s="3">
         <v>200</v>
       </c>
       <c r="Q45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
@@ -3974,10 +4073,10 @@
         <v>100</v>
       </c>
       <c r="U45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W45" s="3">
         <v>100</v>
@@ -3986,10 +4085,10 @@
         <v>100</v>
       </c>
       <c r="Y45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
         <v>100</v>
@@ -3998,14 +4097,14 @@
         <v>100</v>
       </c>
       <c r="AC45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
       <c r="AF45" s="3">
         <v>0</v>
       </c>
@@ -4015,67 +4114,70 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>500</v>
+      </c>
+      <c r="E46" s="3">
         <v>700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>100</v>
-      </c>
-      <c r="S46" s="3">
-        <v>200</v>
       </c>
       <c r="T46" s="3">
         <v>200</v>
       </c>
       <c r="U46" s="3">
+        <v>200</v>
+      </c>
+      <c r="V46" s="3">
         <v>400</v>
-      </c>
-      <c r="V46" s="3">
-        <v>100</v>
       </c>
       <c r="W46" s="3">
         <v>100</v>
@@ -4084,37 +4186,40 @@
         <v>100</v>
       </c>
       <c r="Y46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z46" s="3">
         <v>400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4160,8 +4265,8 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
+      <c r="R47" s="3">
+        <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>4</v>
@@ -4178,8 +4283,8 @@
       <c r="W47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -4211,13 +4316,16 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3">
         <v>100</v>
@@ -4229,7 +4337,7 @@
         <v>100</v>
       </c>
       <c r="H48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I48" s="3">
         <v>200</v>
@@ -4244,7 +4352,7 @@
         <v>200</v>
       </c>
       <c r="M48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -4309,8 +4417,11 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4641,15 +4761,15 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4665,8 +4785,8 @@
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -4677,32 +4797,35 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC52" s="3">
         <v>2600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3900</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>100</v>
       </c>
       <c r="AE52" s="3">
         <v>100</v>
       </c>
       <c r="AF52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AG52" s="3">
         <v>200</v>
       </c>
       <c r="AH52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,67 +4922,70 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>600</v>
+      </c>
+      <c r="E54" s="3">
         <v>800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>100</v>
-      </c>
-      <c r="S54" s="3">
-        <v>200</v>
       </c>
       <c r="T54" s="3">
         <v>200</v>
       </c>
       <c r="U54" s="3">
+        <v>200</v>
+      </c>
+      <c r="V54" s="3">
         <v>400</v>
-      </c>
-      <c r="V54" s="3">
-        <v>100</v>
       </c>
       <c r="W54" s="3">
         <v>100</v>
@@ -4868,37 +4994,40 @@
         <v>100</v>
       </c>
       <c r="Y54" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z54" s="3">
         <v>400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1200</v>
-      </c>
-      <c r="AG54" s="3">
-        <v>700</v>
       </c>
       <c r="AH54" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,221 +5099,228 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
-      </c>
-      <c r="M57" s="3">
-        <v>700</v>
       </c>
       <c r="N57" s="3">
         <v>700</v>
       </c>
       <c r="O57" s="3">
+        <v>700</v>
+      </c>
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>800</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>400</v>
       </c>
       <c r="Z57" s="3">
         <v>400</v>
       </c>
       <c r="AA57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB57" s="3">
         <v>500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>600</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>800</v>
       </c>
       <c r="AF57" s="3">
         <v>800</v>
       </c>
       <c r="AG57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AH57" s="3">
         <v>700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>200</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1400</v>
       </c>
       <c r="G58" s="3">
         <v>1400</v>
       </c>
       <c r="H58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>800</v>
-      </c>
-      <c r="M58" s="3">
-        <v>200</v>
       </c>
       <c r="N58" s="3">
         <v>200</v>
       </c>
       <c r="O58" s="3">
+        <v>200</v>
+      </c>
+      <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5300</v>
-      </c>
-      <c r="S58" s="3">
-        <v>5200</v>
       </c>
       <c r="T58" s="3">
         <v>5200</v>
       </c>
       <c r="U58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="V58" s="3">
         <v>5300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>19700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>18600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>18300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>16400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>17000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>7500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
         <v>1500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1200</v>
       </c>
       <c r="G59" s="3">
         <v>1200</v>
       </c>
       <c r="H59" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="I59" s="3">
         <v>1300</v>
@@ -5192,177 +5329,183 @@
         <v>1300</v>
       </c>
       <c r="K59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L59" s="3">
         <v>1700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E60" s="3">
         <v>3100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>24800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>22700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>21900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>19600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>18800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>11200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5400,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>100</v>
@@ -5415,7 +5558,7 @@
         <v>100</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -5439,42 +5582,45 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>16500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>12100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>14200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>14100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
         <v>100</v>
@@ -5486,14 +5632,14 @@
         <v>100</v>
       </c>
       <c r="K62" s="3">
+        <v>100</v>
+      </c>
+      <c r="L62" s="3">
         <v>200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -5506,14 +5652,14 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>24800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>21900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>22300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>16600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-133100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-124900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-123600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-121700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-119800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-117800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-115800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-113200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-112300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-110300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-108200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-104700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-103100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-101300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-99100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-97200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-93700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-92500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-90000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-85800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-84000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-81500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-78400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-75400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-71200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-67700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-63800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-59900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-57100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-55600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-53800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,8 +6952,11 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6778,97 +6964,100 @@
         <v>-2300</v>
       </c>
       <c r="E76" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F76" s="3">
         <v>-2200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-3100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1700</v>
       </c>
-      <c r="I76" s="3">
-        <v>0</v>
-      </c>
       <c r="J76" s="3">
+        <v>0</v>
+      </c>
+      <c r="K76" s="3">
         <v>1500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-11300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-11100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-10000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-9100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-8300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-10900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-11200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-24700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-22300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-21600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-18800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-19600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-16300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-16600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-15300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-13600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-3100</v>
       </c>
       <c r="Y81" s="3">
         <v>-3100</v>
       </c>
       <c r="Z81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>500</v>
+      </c>
+      <c r="E100" s="3">
         <v>1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-200</v>
       </c>
       <c r="K100" s="3">
         <v>-200</v>
       </c>
       <c r="L100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>1700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>12700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>500</v>
-      </c>
-      <c r="S100" s="3">
-        <v>400</v>
       </c>
       <c r="T100" s="3">
         <v>400</v>
       </c>
       <c r="U100" s="3">
+        <v>400</v>
+      </c>
+      <c r="V100" s="3">
         <v>1000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,8 +9189,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8949,93 +9201,96 @@
         <v>-100</v>
       </c>
       <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-1600</v>
       </c>
       <c r="I102" s="3">
         <v>-1600</v>
       </c>
       <c r="J102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>10700</v>
-      </c>
-      <c r="P102" s="3">
-        <v>100</v>
       </c>
       <c r="Q102" s="3">
         <v>100</v>
       </c>
       <c r="R102" s="3">
+        <v>100</v>
+      </c>
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>300</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
   <si>
     <t>ZIVO</t>
   </si>
@@ -656,159 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -822,8 +826,8 @@
       <c r="I8" s="3">
         <v>0</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -900,16 +904,19 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -920,8 +927,8 @@
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
+      <c r="I9" s="3">
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>4</v>
@@ -1001,16 +1008,19 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -1021,8 +1031,8 @@
       <c r="H10" s="3">
         <v>0</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
+      <c r="I10" s="3">
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>4</v>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
         <v>2300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>300</v>
       </c>
       <c r="F12" s="3">
         <v>300</v>
       </c>
       <c r="G12" s="3">
+        <v>300</v>
+      </c>
+      <c r="H12" s="3">
         <v>200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>400</v>
       </c>
       <c r="I12" s="3">
         <v>400</v>
       </c>
       <c r="J12" s="3">
+        <v>400</v>
+      </c>
+      <c r="K12" s="3">
         <v>500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1600</v>
-      </c>
-      <c r="V12" s="3">
-        <v>500</v>
       </c>
       <c r="W12" s="3">
         <v>500</v>
       </c>
       <c r="X12" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y12" s="3">
         <v>900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>400</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>600</v>
       </c>
       <c r="AA12" s="3">
         <v>600</v>
       </c>
       <c r="AB12" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC12" s="3">
         <v>800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1364,27 +1384,27 @@
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1400,8 +1420,8 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1434,16 +1454,19 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>400</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E17" s="3">
         <v>8200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-2300</v>
       </c>
       <c r="E18" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,31 +1849,32 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1885,141 +1919,147 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3">
         <v>-400</v>
       </c>
       <c r="AA20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-300</v>
       </c>
       <c r="AH20" s="3">
         <v>-300</v>
       </c>
       <c r="AI20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-2300</v>
       </c>
       <c r="E21" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-2000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="L21" s="3">
         <v>-2000</v>
       </c>
-      <c r="J21" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="N21" s="3">
         <v>-2000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="O21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="R21" s="3">
         <v>-2100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="S21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="W21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="X21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-2000</v>
       </c>
-      <c r="N21" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="Z21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-1600</v>
       </c>
-      <c r="P21" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="AD21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-2100</v>
       </c>
-      <c r="R21" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="AF21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-1000</v>
       </c>
-      <c r="U21" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AH21" s="3">
-        <v>-900</v>
       </c>
       <c r="AI21" s="3">
         <v>-900</v>
       </c>
+      <c r="AJ21" s="3">
+        <v>-900</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2030,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -2060,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
@@ -2078,173 +2118,179 @@
         <v>100</v>
       </c>
       <c r="V22" s="3">
+        <v>100</v>
+      </c>
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>500</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>400</v>
       </c>
       <c r="AG22" s="3">
         <v>400</v>
       </c>
       <c r="AH22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI22" s="3">
         <v>300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-3100</v>
       </c>
       <c r="Z23" s="3">
         <v>-3100</v>
       </c>
       <c r="AA23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-3100</v>
       </c>
       <c r="Z26" s="3">
         <v>-3100</v>
       </c>
       <c r="AA26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-3100</v>
       </c>
       <c r="Z27" s="3">
         <v>-3100</v>
       </c>
       <c r="AA27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,31 +3095,34 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3097,141 +3167,147 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3">
         <v>400</v>
       </c>
       <c r="AA32" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB32" s="3">
         <v>300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>100</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>300</v>
       </c>
       <c r="AH32" s="3">
         <v>300</v>
       </c>
       <c r="AI32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-3100</v>
       </c>
       <c r="Z33" s="3">
         <v>-3100</v>
       </c>
       <c r="AA33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-3100</v>
       </c>
       <c r="Z35" s="3">
         <v>-3100</v>
       </c>
       <c r="AA35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,55 +3698,56 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1500</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>200</v>
-      </c>
-      <c r="R41" s="3">
-        <v>100</v>
       </c>
       <c r="S41" s="3">
         <v>100</v>
@@ -3669,14 +3756,14 @@
         <v>100</v>
       </c>
       <c r="U41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
         <v>300</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
       <c r="X41" s="3">
         <v>0</v>
       </c>
@@ -3684,37 +3771,40 @@
         <v>0</v>
       </c>
       <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
         <v>400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1200</v>
       </c>
-      <c r="AF41" s="3">
-        <v>0</v>
-      </c>
       <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
         <v>1000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,16 +3904,19 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
         <v>0</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
@@ -3831,8 +3924,8 @@
       <c r="G43" s="3">
         <v>0</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
+      <c r="H43" s="3">
+        <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
@@ -3849,8 +3942,8 @@
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -3867,14 +3960,14 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>4</v>
@@ -3891,8 +3984,8 @@
       <c r="AA43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -3915,31 +4008,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,58 +4112,61 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
+        <v>100</v>
+      </c>
+      <c r="L45" s="3">
+        <v>300</v>
+      </c>
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
-        <v>600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>500</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>900</v>
-      </c>
-      <c r="N45" s="3">
-        <v>100</v>
       </c>
       <c r="O45" s="3">
         <v>100</v>
       </c>
       <c r="P45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q45" s="3">
         <v>200</v>
       </c>
       <c r="R45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3">
         <v>100</v>
@@ -4076,10 +4175,10 @@
         <v>100</v>
       </c>
       <c r="V45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3">
         <v>100</v>
@@ -4088,10 +4187,10 @@
         <v>100</v>
       </c>
       <c r="Z45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="3">
         <v>100</v>
@@ -4100,14 +4199,14 @@
         <v>100</v>
       </c>
       <c r="AD45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
-      <c r="AF45" s="3">
-        <v>0</v>
-      </c>
       <c r="AG45" s="3">
         <v>0</v>
       </c>
@@ -4117,70 +4216,73 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>400</v>
+      </c>
+      <c r="E46" s="3">
         <v>500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>100</v>
-      </c>
-      <c r="T46" s="3">
-        <v>200</v>
       </c>
       <c r="U46" s="3">
         <v>200</v>
       </c>
       <c r="V46" s="3">
+        <v>200</v>
+      </c>
+      <c r="W46" s="3">
         <v>400</v>
-      </c>
-      <c r="W46" s="3">
-        <v>100</v>
       </c>
       <c r="X46" s="3">
         <v>100</v>
@@ -4189,60 +4291,63 @@
         <v>100</v>
       </c>
       <c r="Z46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA46" s="3">
         <v>400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4268,8 +4373,8 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
+      <c r="S47" s="3">
+        <v>0</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>4</v>
@@ -4286,8 +4391,8 @@
       <c r="X47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -4319,8 +4424,11 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4328,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3">
         <v>100</v>
@@ -4340,7 +4448,7 @@
         <v>100</v>
       </c>
       <c r="I48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>200</v>
@@ -4355,7 +4463,7 @@
         <v>200</v>
       </c>
       <c r="N48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -4420,8 +4528,11 @@
       <c r="AI48" s="3">
         <v>0</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,8 +4840,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4764,15 +4884,15 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q52" s="3">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4788,8 +4908,8 @@
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4800,32 +4920,35 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD52" s="3">
         <v>2600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3900</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>100</v>
       </c>
       <c r="AF52" s="3">
         <v>100</v>
       </c>
       <c r="AG52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AH52" s="3">
         <v>200</v>
       </c>
       <c r="AI52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,70 +5048,73 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>500</v>
+      </c>
+      <c r="E54" s="3">
         <v>600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>100</v>
-      </c>
-      <c r="T54" s="3">
-        <v>200</v>
       </c>
       <c r="U54" s="3">
         <v>200</v>
       </c>
       <c r="V54" s="3">
+        <v>200</v>
+      </c>
+      <c r="W54" s="3">
         <v>400</v>
-      </c>
-      <c r="W54" s="3">
-        <v>100</v>
       </c>
       <c r="X54" s="3">
         <v>100</v>
@@ -4997,37 +5123,40 @@
         <v>100</v>
       </c>
       <c r="Z54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA54" s="3">
         <v>400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1200</v>
-      </c>
-      <c r="AH54" s="3">
-        <v>700</v>
       </c>
       <c r="AI54" s="3">
         <v>700</v>
       </c>
+      <c r="AJ54" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,412 +5230,425 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
-      </c>
-      <c r="N57" s="3">
-        <v>700</v>
       </c>
       <c r="O57" s="3">
         <v>700</v>
       </c>
       <c r="P57" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>800</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>400</v>
       </c>
       <c r="AA57" s="3">
         <v>400</v>
       </c>
       <c r="AB57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>600</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>800</v>
       </c>
       <c r="AG57" s="3">
         <v>800</v>
       </c>
       <c r="AH57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AI57" s="3">
         <v>700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F58" s="3">
+        <v>800</v>
+      </c>
+      <c r="G58" s="3">
+        <v>300</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>900</v>
+      </c>
+      <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="G58" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
+        <v>400</v>
+      </c>
+      <c r="M58" s="3">
+        <v>600</v>
+      </c>
+      <c r="N58" s="3">
         <v>800</v>
-      </c>
-      <c r="J58" s="3">
-        <v>200</v>
-      </c>
-      <c r="K58" s="3">
-        <v>400</v>
-      </c>
-      <c r="L58" s="3">
-        <v>600</v>
-      </c>
-      <c r="M58" s="3">
-        <v>800</v>
-      </c>
-      <c r="N58" s="3">
-        <v>200</v>
       </c>
       <c r="O58" s="3">
         <v>200</v>
       </c>
       <c r="P58" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q58" s="3">
         <v>300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5300</v>
-      </c>
-      <c r="T58" s="3">
-        <v>5200</v>
       </c>
       <c r="U58" s="3">
         <v>5200</v>
       </c>
       <c r="V58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="W58" s="3">
         <v>5300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>19700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>18600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>18300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>16400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>17000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>7500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1200</v>
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H59" s="3">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="I59" s="3">
-        <v>1300</v>
+        <v>300</v>
       </c>
       <c r="J59" s="3">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="K59" s="3">
         <v>1300</v>
       </c>
       <c r="L59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M59" s="3">
         <v>1700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>24800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>22700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>21900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>19600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>18800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>11200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5525,10 +5668,10 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5546,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>100</v>
@@ -5561,7 +5704,7 @@
         <v>100</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
@@ -5585,28 +5728,31 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>16500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>12100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>14200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>14100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5616,33 +5762,33 @@
       <c r="E62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>100</v>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>100</v>
       </c>
       <c r="L62" s="3">
+        <v>100</v>
+      </c>
+      <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
@@ -5655,14 +5801,14 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>24800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>21900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>22300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>16800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-135400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-133100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-124900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-123600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-121700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-119800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-117800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-115800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-113200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-112300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-110300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-108200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-104700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-103100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-101300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-99100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-97200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-93700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-92500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-90000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-85800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-84000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-81500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-78400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-75400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-71200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-67700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-63800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-59900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-57100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-55600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-53800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-2300</v>
+        <v>-2100</v>
       </c>
       <c r="E76" s="3">
         <v>-2300</v>
       </c>
       <c r="F76" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G76" s="3">
         <v>-2200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-3100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1700</v>
       </c>
-      <c r="J76" s="3">
-        <v>0</v>
-      </c>
       <c r="K76" s="3">
+        <v>0</v>
+      </c>
+      <c r="L76" s="3">
         <v>1500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-11400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-11300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-11100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-10000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-9100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-8300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-10900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-24700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-22300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-21600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-18800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-19600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-16300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-16600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-15300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-13600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-3100</v>
       </c>
       <c r="Z81" s="3">
         <v>-3100</v>
       </c>
       <c r="AA81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,31 +7599,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,31 +8365,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,31 +8675,34 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -8549,8 +8779,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,132 +9233,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-200</v>
       </c>
       <c r="L100" s="3">
         <v>-200</v>
       </c>
       <c r="M100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>1700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>12700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>500</v>
-      </c>
-      <c r="T100" s="3">
-        <v>400</v>
       </c>
       <c r="U100" s="3">
         <v>400</v>
       </c>
       <c r="V100" s="3">
+        <v>400</v>
+      </c>
+      <c r="W100" s="3">
         <v>1000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="E102" s="3">
         <v>-100</v>
       </c>
       <c r="F102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-1600</v>
       </c>
       <c r="J102" s="3">
         <v>-1600</v>
       </c>
       <c r="K102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="L102" s="3">
         <v>-1700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>10700</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>100</v>
       </c>
       <c r="R102" s="3">
         <v>100</v>
       </c>
       <c r="S102" s="3">
+        <v>100</v>
+      </c>
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
         <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>ZIVO</t>
   </si>
@@ -656,166 +656,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -826,11 +829,11 @@
       <c r="I8" s="3">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -907,19 +910,22 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -930,8 +936,8 @@
       <c r="I9" s="3">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+      <c r="J9" s="3">
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
@@ -1011,19 +1017,22 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0</v>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
@@ -1034,8 +1043,8 @@
       <c r="I10" s="3">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="J10" s="3">
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -1115,8 +1124,11 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,112 +1165,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
         <v>300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2300</v>
-      </c>
-      <c r="F12" s="3">
-        <v>300</v>
       </c>
       <c r="G12" s="3">
         <v>300</v>
       </c>
       <c r="H12" s="3">
+        <v>300</v>
+      </c>
+      <c r="I12" s="3">
         <v>200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>400</v>
       </c>
       <c r="J12" s="3">
         <v>400</v>
       </c>
       <c r="K12" s="3">
+        <v>400</v>
+      </c>
+      <c r="L12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1600</v>
-      </c>
-      <c r="W12" s="3">
-        <v>500</v>
       </c>
       <c r="X12" s="3">
         <v>500</v>
       </c>
       <c r="Y12" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z12" s="3">
         <v>900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>400</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>600</v>
       </c>
       <c r="AB12" s="3">
         <v>600</v>
       </c>
       <c r="AC12" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD12" s="3">
         <v>800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,27 +1406,27 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1423,8 +1442,8 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1457,16 +1476,19 @@
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>400</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ14" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,25 +1882,26 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
@@ -1876,8 +1909,8 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1922,144 +1955,150 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>-400</v>
       </c>
       <c r="AB20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>-300</v>
       </c>
       <c r="AI20" s="3">
         <v>-300</v>
       </c>
       <c r="AJ20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AI21" s="3">
-        <v>-900</v>
       </c>
       <c r="AJ21" s="3">
         <v>-900</v>
       </c>
+      <c r="AK21" s="3">
+        <v>-900</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2103,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R22" s="3">
         <v>100</v>
@@ -2121,153 +2160,159 @@
         <v>100</v>
       </c>
       <c r="W22" s="3">
+        <v>100</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>500</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>400</v>
       </c>
       <c r="AH22" s="3">
         <v>400</v>
       </c>
       <c r="AI22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-3100</v>
       </c>
       <c r="AA23" s="3">
         <v>-3100</v>
       </c>
       <c r="AB23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,8 +2337,8 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2370,8 +2415,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-3100</v>
       </c>
       <c r="AA26" s="3">
         <v>-3100</v>
       </c>
       <c r="AB26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-3100</v>
       </c>
       <c r="AA27" s="3">
         <v>-3100</v>
       </c>
       <c r="AB27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,25 +3164,28 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>0</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
@@ -3124,8 +3193,8 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -3170,144 +3239,150 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>400</v>
       </c>
       <c r="AB32" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC32" s="3">
         <v>300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>100</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>300</v>
       </c>
       <c r="AI32" s="3">
         <v>300</v>
       </c>
       <c r="AJ32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-3100</v>
       </c>
       <c r="AA33" s="3">
         <v>-3100</v>
       </c>
       <c r="AB33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-3100</v>
       </c>
       <c r="AA35" s="3">
         <v>-3100</v>
       </c>
       <c r="AB35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,58 +3784,59 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1500</v>
       </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
       <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>200</v>
-      </c>
-      <c r="S41" s="3">
-        <v>100</v>
       </c>
       <c r="T41" s="3">
         <v>100</v>
@@ -3759,14 +3845,14 @@
         <v>100</v>
       </c>
       <c r="V41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>300</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
       <c r="Y41" s="3">
         <v>0</v>
       </c>
@@ -3774,37 +3860,40 @@
         <v>0</v>
       </c>
       <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="3">
         <v>400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1200</v>
       </c>
-      <c r="AG41" s="3">
-        <v>0</v>
-      </c>
       <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3">
         <v>1000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,19 +3996,22 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
         <v>0</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
@@ -3927,8 +4019,8 @@
       <c r="H43" s="3">
         <v>0</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
+      <c r="I43" s="3">
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
@@ -3945,8 +4037,8 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3963,14 +4055,14 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>4</v>
@@ -3987,8 +4079,8 @@
       <c r="AB43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -4011,8 +4103,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,8 +4210,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4141,35 +4239,35 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
-      </c>
-      <c r="O45" s="3">
-        <v>100</v>
       </c>
       <c r="P45" s="3">
         <v>100</v>
       </c>
       <c r="Q45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3">
         <v>100</v>
@@ -4178,10 +4276,10 @@
         <v>100</v>
       </c>
       <c r="W45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>100</v>
@@ -4190,10 +4288,10 @@
         <v>100</v>
       </c>
       <c r="AA45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC45" s="3">
         <v>100</v>
@@ -4202,14 +4300,14 @@
         <v>100</v>
       </c>
       <c r="AE45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
         <v>100</v>
       </c>
-      <c r="AG45" s="3">
-        <v>0</v>
-      </c>
       <c r="AH45" s="3">
         <v>0</v>
       </c>
@@ -4219,73 +4317,76 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E46" s="3">
         <v>400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>100</v>
-      </c>
-      <c r="U46" s="3">
-        <v>200</v>
       </c>
       <c r="V46" s="3">
         <v>200</v>
       </c>
       <c r="W46" s="3">
+        <v>200</v>
+      </c>
+      <c r="X46" s="3">
         <v>400</v>
-      </c>
-      <c r="X46" s="3">
-        <v>100</v>
       </c>
       <c r="Y46" s="3">
         <v>100</v>
@@ -4294,37 +4395,40 @@
         <v>100</v>
       </c>
       <c r="AA46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB46" s="3">
         <v>400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4349,8 +4453,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4376,8 +4480,8 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
+      <c r="T47" s="3">
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>4</v>
@@ -4394,8 +4498,8 @@
       <c r="Y47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -4427,19 +4531,22 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E48" s="3">
         <v>0</v>
       </c>
       <c r="F48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3">
         <v>100</v>
@@ -4451,7 +4558,7 @@
         <v>100</v>
       </c>
       <c r="J48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
@@ -4466,7 +4573,7 @@
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -4531,8 +4638,11 @@
       <c r="AJ48" s="3">
         <v>0</v>
       </c>
+      <c r="AK48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +4959,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4887,15 +5006,15 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R52" s="3">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4911,8 +5030,8 @@
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -4923,32 +5042,35 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE52" s="3">
         <v>2600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3900</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>100</v>
       </c>
       <c r="AG52" s="3">
         <v>100</v>
       </c>
       <c r="AH52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AI52" s="3">
         <v>200</v>
       </c>
       <c r="AJ52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,73 +5173,76 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E54" s="3">
         <v>500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>100</v>
-      </c>
-      <c r="U54" s="3">
-        <v>200</v>
       </c>
       <c r="V54" s="3">
         <v>200</v>
       </c>
       <c r="W54" s="3">
+        <v>200</v>
+      </c>
+      <c r="X54" s="3">
         <v>400</v>
-      </c>
-      <c r="X54" s="3">
-        <v>100</v>
       </c>
       <c r="Y54" s="3">
         <v>100</v>
@@ -5126,37 +5251,40 @@
         <v>100</v>
       </c>
       <c r="AA54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB54" s="3">
         <v>400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1200</v>
-      </c>
-      <c r="AI54" s="3">
-        <v>700</v>
       </c>
       <c r="AJ54" s="3">
         <v>700</v>
       </c>
+      <c r="AK54" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,429 +5360,442 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
-      </c>
-      <c r="O57" s="3">
-        <v>700</v>
       </c>
       <c r="P57" s="3">
         <v>700</v>
       </c>
       <c r="Q57" s="3">
+        <v>700</v>
+      </c>
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>800</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>400</v>
       </c>
       <c r="AB57" s="3">
         <v>400</v>
       </c>
       <c r="AC57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>600</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>800</v>
       </c>
       <c r="AH57" s="3">
         <v>800</v>
       </c>
       <c r="AI57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>100</v>
+      </c>
+      <c r="E58" s="3">
         <v>400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1500</v>
       </c>
       <c r="I58" s="3">
         <v>1500</v>
       </c>
       <c r="J58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K58" s="3">
         <v>900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>800</v>
-      </c>
-      <c r="O58" s="3">
-        <v>200</v>
       </c>
       <c r="P58" s="3">
         <v>200</v>
       </c>
       <c r="Q58" s="3">
+        <v>200</v>
+      </c>
+      <c r="R58" s="3">
         <v>300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5300</v>
-      </c>
-      <c r="U58" s="3">
-        <v>5200</v>
       </c>
       <c r="V58" s="3">
         <v>5200</v>
       </c>
       <c r="W58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="X58" s="3">
         <v>5300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>19700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>18600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>18300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>16400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>17000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
+      <c r="F59" s="3">
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1300</v>
       </c>
       <c r="L59" s="3">
         <v>1300</v>
       </c>
       <c r="M59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N59" s="3">
         <v>1700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>24800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>22700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>21900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>19600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>18800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>11200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -5668,13 +5810,13 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -5692,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>100</v>
@@ -5707,7 +5849,7 @@
         <v>100</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -5731,28 +5873,31 @@
         <v>0</v>
       </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>16500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>12100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>14200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>14100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5777,21 +5922,21 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>100</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>100</v>
       </c>
       <c r="M62" s="3">
+        <v>100</v>
+      </c>
+      <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -5804,14 +5949,14 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
+      <c r="T62" s="3">
+        <v>0</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -5855,8 +6000,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>24800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>22700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>22300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>16600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>14400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-137000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-135400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-133100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-124900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-123600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-121700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-119800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-117800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-115800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-113200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-112300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-110300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-108200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-104700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-103100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-101300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-99100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-97200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-93700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-92500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-90000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-85800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-81500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-78400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-75400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-71200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-67700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-63800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-59900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-57100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-55600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-53800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2100</v>
-      </c>
-      <c r="E76" s="3">
-        <v>-2300</v>
       </c>
       <c r="F76" s="3">
         <v>-2300</v>
       </c>
       <c r="G76" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H76" s="3">
         <v>-2200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-3100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1700</v>
       </c>
-      <c r="K76" s="3">
-        <v>0</v>
-      </c>
       <c r="L76" s="3">
+        <v>0</v>
+      </c>
+      <c r="M76" s="3">
         <v>1500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-11400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-11300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-11100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-10000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-9100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-8300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-24700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-22300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-21600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-18800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-19600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-16300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-16600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-15300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-13600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2500</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-3100</v>
       </c>
       <c r="AA81" s="3">
         <v>-3100</v>
       </c>
       <c r="AB81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7797,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7626,8 +7824,8 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -7704,8 +7902,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8585,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8392,8 +8612,8 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8470,8 +8690,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,8 +8904,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8704,8 +8933,8 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -8782,8 +9011,11 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,112 +9478,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E100" s="3">
         <v>1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-200</v>
       </c>
       <c r="M100" s="3">
         <v>-200</v>
       </c>
       <c r="N100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>1700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>12700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>500</v>
-      </c>
-      <c r="U100" s="3">
-        <v>400</v>
       </c>
       <c r="V100" s="3">
         <v>400</v>
       </c>
       <c r="W100" s="3">
+        <v>400</v>
+      </c>
+      <c r="X100" s="3">
         <v>1000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,108 +9692,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-100</v>
       </c>
       <c r="F102" s="3">
         <v>-100</v>
       </c>
       <c r="G102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-1600</v>
       </c>
       <c r="K102" s="3">
         <v>-1600</v>
       </c>
       <c r="L102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="M102" s="3">
         <v>-1700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>10700</v>
-      </c>
-      <c r="R102" s="3">
-        <v>100</v>
       </c>
       <c r="S102" s="3">
         <v>100</v>
       </c>
       <c r="T102" s="3">
+        <v>100</v>
+      </c>
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>ZIVO</t>
   </si>
@@ -656,158 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -815,13 +819,13 @@
         <v>4</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H8" s="3">
         <v>0</v>
@@ -832,11 +836,11 @@
       <c r="J8" s="3">
         <v>0</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -913,22 +917,25 @@
       <c r="AK8" s="3">
         <v>0</v>
       </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
@@ -939,8 +946,8 @@
       <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
+      <c r="K9" s="3">
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
@@ -1020,22 +1027,25 @@
       <c r="AK9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -1046,8 +1056,8 @@
       <c r="J10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
+      <c r="K10" s="3">
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
@@ -1127,8 +1137,11 @@
       <c r="AK10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,115 +1179,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2300</v>
-      </c>
-      <c r="G12" s="3">
-        <v>300</v>
       </c>
       <c r="H12" s="3">
         <v>300</v>
       </c>
       <c r="I12" s="3">
+        <v>300</v>
+      </c>
+      <c r="J12" s="3">
         <v>200</v>
-      </c>
-      <c r="J12" s="3">
-        <v>400</v>
       </c>
       <c r="K12" s="3">
         <v>400</v>
       </c>
       <c r="L12" s="3">
+        <v>400</v>
+      </c>
+      <c r="M12" s="3">
         <v>500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1600</v>
-      </c>
-      <c r="X12" s="3">
-        <v>500</v>
       </c>
       <c r="Y12" s="3">
         <v>500</v>
       </c>
       <c r="Z12" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA12" s="3">
         <v>900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>400</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>600</v>
       </c>
       <c r="AC12" s="3">
         <v>600</v>
       </c>
       <c r="AD12" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE12" s="3">
         <v>800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>300</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,27 +1429,27 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1445,8 +1465,8 @@
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1479,16 +1499,19 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>400</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK14" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,22 +1916,23 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1912,8 +1946,8 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1958,147 +1992,153 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>-400</v>
       </c>
       <c r="AC20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>-300</v>
       </c>
       <c r="AJ20" s="3">
         <v>-300</v>
       </c>
       <c r="AK20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AJ21" s="3">
-        <v>-900</v>
       </c>
       <c r="AK21" s="3">
         <v>-900</v>
       </c>
+      <c r="AL21" s="3">
+        <v>-900</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2145,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3">
         <v>100</v>
@@ -2163,156 +2203,162 @@
         <v>100</v>
       </c>
       <c r="X22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>500</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>400</v>
       </c>
       <c r="AI22" s="3">
         <v>400</v>
       </c>
       <c r="AJ22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK22" s="3">
         <v>300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-3100</v>
       </c>
       <c r="AB23" s="3">
         <v>-3100</v>
       </c>
       <c r="AC23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2340,8 +2386,8 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2418,8 +2464,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-3100</v>
       </c>
       <c r="AB26" s="3">
         <v>-3100</v>
       </c>
       <c r="AC26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-3100</v>
       </c>
       <c r="AB27" s="3">
         <v>-3100</v>
       </c>
       <c r="AC27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,22 +3234,25 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -3196,8 +3266,8 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3242,147 +3312,153 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>400</v>
       </c>
       <c r="AC32" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD32" s="3">
         <v>300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>100</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>300</v>
       </c>
       <c r="AJ32" s="3">
         <v>300</v>
       </c>
       <c r="AK32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-3100</v>
       </c>
       <c r="AB33" s="3">
         <v>-3100</v>
       </c>
       <c r="AC33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-3100</v>
       </c>
       <c r="AB35" s="3">
         <v>-3100</v>
       </c>
       <c r="AC35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,61 +3871,62 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
       <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1500</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
       <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
         <v>200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>200</v>
-      </c>
-      <c r="T41" s="3">
-        <v>100</v>
       </c>
       <c r="U41" s="3">
         <v>100</v>
@@ -3848,14 +3935,14 @@
         <v>100</v>
       </c>
       <c r="W41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
         <v>300</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
       <c r="Z41" s="3">
         <v>0</v>
       </c>
@@ -3863,37 +3950,40 @@
         <v>0</v>
       </c>
       <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="3">
         <v>400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1200</v>
       </c>
-      <c r="AH41" s="3">
-        <v>0</v>
-      </c>
       <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3999,22 +4089,25 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
+      <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H43" s="3">
         <v>0</v>
@@ -4022,8 +4115,8 @@
       <c r="I43" s="3">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
+      <c r="J43" s="3">
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
@@ -4040,8 +4133,8 @@
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -4058,14 +4151,14 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>4</v>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>4</v>
@@ -4082,8 +4175,8 @@
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE43" s="3">
         <v>0</v>
@@ -4106,8 +4199,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,8 +4309,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4242,35 +4341,35 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>100</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
       </c>
       <c r="R45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S45" s="3">
         <v>200</v>
       </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3">
         <v>100</v>
@@ -4279,10 +4378,10 @@
         <v>100</v>
       </c>
       <c r="X45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3">
         <v>100</v>
@@ -4291,10 +4390,10 @@
         <v>100</v>
       </c>
       <c r="AB45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD45" s="3">
         <v>100</v>
@@ -4303,14 +4402,14 @@
         <v>100</v>
       </c>
       <c r="AF45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3">
         <v>100</v>
       </c>
-      <c r="AH45" s="3">
-        <v>0</v>
-      </c>
       <c r="AI45" s="3">
         <v>0</v>
       </c>
@@ -4320,76 +4419,79 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>100</v>
-      </c>
-      <c r="V46" s="3">
-        <v>200</v>
       </c>
       <c r="W46" s="3">
         <v>200</v>
       </c>
       <c r="X46" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y46" s="3">
         <v>400</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>100</v>
       </c>
       <c r="Z46" s="3">
         <v>100</v>
@@ -4398,37 +4500,40 @@
         <v>100</v>
       </c>
       <c r="AB46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC46" s="3">
         <v>400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4456,8 +4561,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4483,8 +4588,8 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
+      <c r="U47" s="3">
+        <v>0</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>4</v>
@@ -4501,8 +4606,8 @@
       <c r="Z47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -4534,22 +4639,25 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
+      <c r="D48" s="3">
+        <v>300</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F48" s="3">
         <v>0</v>
       </c>
       <c r="G48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
         <v>100</v>
@@ -4561,7 +4669,7 @@
         <v>100</v>
       </c>
       <c r="K48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L48" s="3">
         <v>200</v>
@@ -4576,7 +4684,7 @@
         <v>200</v>
       </c>
       <c r="P48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -4641,8 +4749,11 @@
       <c r="AK48" s="3">
         <v>0</v>
       </c>
+      <c r="AL48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,8 +5079,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5009,15 +5129,15 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S52" s="3">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
@@ -5033,8 +5153,8 @@
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -5045,32 +5165,35 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF52" s="3">
         <v>2600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3900</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>100</v>
       </c>
       <c r="AH52" s="3">
         <v>100</v>
       </c>
       <c r="AI52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AJ52" s="3">
         <v>200</v>
       </c>
       <c r="AK52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,76 +5299,79 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>100</v>
-      </c>
-      <c r="V54" s="3">
-        <v>200</v>
       </c>
       <c r="W54" s="3">
         <v>200</v>
       </c>
       <c r="X54" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y54" s="3">
         <v>400</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>100</v>
       </c>
       <c r="Z54" s="3">
         <v>100</v>
@@ -5254,37 +5380,40 @@
         <v>100</v>
       </c>
       <c r="AB54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC54" s="3">
         <v>400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1200</v>
-      </c>
-      <c r="AJ54" s="3">
-        <v>700</v>
       </c>
       <c r="AK54" s="3">
         <v>700</v>
       </c>
+      <c r="AL54" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,8 +5491,9 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5370,436 +5501,448 @@
         <v>700</v>
       </c>
       <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
-      </c>
-      <c r="P57" s="3">
-        <v>700</v>
       </c>
       <c r="Q57" s="3">
         <v>700</v>
       </c>
       <c r="R57" s="3">
+        <v>700</v>
+      </c>
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>800</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>400</v>
       </c>
       <c r="AC57" s="3">
         <v>400</v>
       </c>
       <c r="AD57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE57" s="3">
         <v>500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>600</v>
-      </c>
-      <c r="AH57" s="3">
-        <v>800</v>
       </c>
       <c r="AI57" s="3">
         <v>800</v>
       </c>
       <c r="AJ57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AK57" s="3">
         <v>700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
         <v>100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1500</v>
       </c>
       <c r="J58" s="3">
         <v>1500</v>
       </c>
       <c r="K58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L58" s="3">
         <v>900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>800</v>
-      </c>
-      <c r="P58" s="3">
-        <v>200</v>
       </c>
       <c r="Q58" s="3">
         <v>200</v>
       </c>
       <c r="R58" s="3">
+        <v>200</v>
+      </c>
+      <c r="S58" s="3">
         <v>300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5300</v>
-      </c>
-      <c r="V58" s="3">
-        <v>5200</v>
       </c>
       <c r="W58" s="3">
         <v>5200</v>
       </c>
       <c r="X58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="Y58" s="3">
         <v>5300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>19700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>18600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>18300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>16400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>17000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>7500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
+      <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F59" s="3">
         <v>0</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
+      <c r="G59" s="3">
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1300</v>
       </c>
       <c r="M59" s="3">
         <v>1300</v>
       </c>
       <c r="N59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O59" s="3">
         <v>1700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>24800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>22700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>21900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>19600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>11200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
         <v>100</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -5813,13 +5956,13 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>100</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5837,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>100</v>
@@ -5852,7 +5995,7 @@
         <v>100</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
@@ -5876,28 +6019,31 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>16500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>12100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>14200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>14100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5925,21 +6071,21 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>100</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
       </c>
       <c r="N62" s="3">
+        <v>100</v>
+      </c>
+      <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -5952,14 +6098,14 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
@@ -6003,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E66" s="3">
         <v>2200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>24800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>22700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>22300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>16600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>16800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>16600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>14400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-141200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-137000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-135400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-133100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-124900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-123600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-121700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-119800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-117800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-115800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-113200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-112300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-110300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-108200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-104700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-103100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-101300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-99100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-97200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-93700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-92500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-90000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-85800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-81500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-78400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-75400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-71200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-67700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-63800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-59900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-57100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-55600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-53800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-2100</v>
-      </c>
-      <c r="F76" s="3">
-        <v>-2300</v>
       </c>
       <c r="G76" s="3">
         <v>-2300</v>
       </c>
       <c r="H76" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="I76" s="3">
         <v>-2200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-3100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1700</v>
       </c>
-      <c r="L76" s="3">
-        <v>0</v>
-      </c>
       <c r="M76" s="3">
+        <v>0</v>
+      </c>
+      <c r="N76" s="3">
         <v>1500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-11400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-11300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-11100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-10000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-9100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-24700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-22300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-21600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-18800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-19600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-16300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-18000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-16600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-15300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-13600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-3100</v>
       </c>
       <c r="AB81" s="3">
         <v>-3100</v>
       </c>
       <c r="AC81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,16 +7996,17 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
+      <c r="E83" s="3">
+        <v>100</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>4</v>
@@ -7827,8 +8026,8 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7905,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,8 +8806,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8615,8 +8836,8 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8693,8 +8914,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,8 +9134,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8936,8 +9166,8 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -9014,8 +9244,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,115 +9724,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
         <v>2300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-200</v>
       </c>
       <c r="N100" s="3">
         <v>-200</v>
       </c>
       <c r="O100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>1700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>12700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>500</v>
-      </c>
-      <c r="V100" s="3">
-        <v>400</v>
       </c>
       <c r="W100" s="3">
         <v>400</v>
       </c>
       <c r="X100" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y100" s="3">
         <v>1000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-100</v>
       </c>
       <c r="G102" s="3">
         <v>-100</v>
       </c>
       <c r="H102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-200</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-1600</v>
       </c>
       <c r="L102" s="3">
         <v>-1600</v>
       </c>
       <c r="M102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N102" s="3">
         <v>-1700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>10700</v>
-      </c>
-      <c r="S102" s="3">
-        <v>100</v>
       </c>
       <c r="T102" s="3">
         <v>100</v>
       </c>
       <c r="U102" s="3">
+        <v>100</v>
+      </c>
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZIVO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>ZIVO</t>
   </si>
@@ -656,179 +656,183 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -839,11 +843,11 @@
       <c r="K8" s="3">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -920,25 +924,28 @@
       <c r="AL8" s="3">
         <v>0</v>
       </c>
+      <c r="AM8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
@@ -949,8 +956,8 @@
       <c r="K9" s="3">
         <v>0</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
+      <c r="L9" s="3">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
@@ -1030,25 +1037,28 @@
       <c r="AL9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
@@ -1059,8 +1069,8 @@
       <c r="K10" s="3">
         <v>0</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
+      <c r="L10" s="3">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
@@ -1140,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,118 +1193,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
         <v>2800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>300</v>
       </c>
       <c r="I12" s="3">
         <v>300</v>
       </c>
       <c r="J12" s="3">
+        <v>300</v>
+      </c>
+      <c r="K12" s="3">
         <v>200</v>
-      </c>
-      <c r="K12" s="3">
-        <v>400</v>
       </c>
       <c r="L12" s="3">
         <v>400</v>
       </c>
       <c r="M12" s="3">
+        <v>400</v>
+      </c>
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1600</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>500</v>
       </c>
       <c r="Z12" s="3">
         <v>500</v>
       </c>
       <c r="AA12" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB12" s="3">
         <v>900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>400</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>600</v>
       </c>
       <c r="AD12" s="3">
         <v>600</v>
       </c>
       <c r="AE12" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF12" s="3">
         <v>800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,27 +1452,27 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-100</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1468,8 +1488,8 @@
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1502,16 +1522,19 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>400</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AL14" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E17" s="3">
         <v>4200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1928,14 +1962,14 @@
       <c r="E20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
@@ -1949,8 +1983,8 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1995,150 +2029,156 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="3">
         <v>-400</v>
       </c>
       <c r="AD20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>-300</v>
       </c>
       <c r="AK20" s="3">
         <v>-300</v>
       </c>
       <c r="AL20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AM20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AK21" s="3">
-        <v>-900</v>
       </c>
       <c r="AL21" s="3">
         <v>-900</v>
       </c>
+      <c r="AM21" s="3">
+        <v>-900</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2188,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3">
         <v>100</v>
@@ -2206,159 +2246,165 @@
         <v>100</v>
       </c>
       <c r="Y22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z22" s="3">
         <v>400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>500</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>400</v>
       </c>
       <c r="AJ22" s="3">
         <v>400</v>
       </c>
       <c r="AK22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AL22" s="3">
         <v>300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-3100</v>
       </c>
       <c r="AC23" s="3">
         <v>-3100</v>
       </c>
       <c r="AD23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2389,8 +2435,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2467,8 +2513,11 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-3100</v>
       </c>
       <c r="AC26" s="3">
         <v>-3100</v>
       </c>
       <c r="AD26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-3100</v>
       </c>
       <c r="AC27" s="3">
         <v>-3100</v>
       </c>
       <c r="AD27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3248,14 +3318,14 @@
       <c r="E32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
@@ -3269,8 +3339,8 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3315,150 +3385,156 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="3">
         <v>400</v>
       </c>
       <c r="AD32" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE32" s="3">
         <v>300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>100</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>300</v>
       </c>
       <c r="AK32" s="3">
         <v>300</v>
       </c>
       <c r="AL32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AM32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-3100</v>
       </c>
       <c r="AC33" s="3">
         <v>-3100</v>
       </c>
       <c r="AD33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-3100</v>
       </c>
       <c r="AC35" s="3">
         <v>-3100</v>
       </c>
       <c r="AD35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,64 +3958,65 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
         <v>500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
       <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>200</v>
-      </c>
-      <c r="U41" s="3">
-        <v>100</v>
       </c>
       <c r="V41" s="3">
         <v>100</v>
@@ -3938,14 +4025,14 @@
         <v>100</v>
       </c>
       <c r="X41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
       <c r="AA41" s="3">
         <v>0</v>
       </c>
@@ -3953,37 +4040,40 @@
         <v>0</v>
       </c>
       <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3">
         <v>400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1200</v>
       </c>
-      <c r="AI41" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3">
         <v>1000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,25 +4182,28 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
@@ -4118,8 +4211,8 @@
       <c r="J43" s="3">
         <v>0</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
+      <c r="K43" s="3">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
@@ -4136,8 +4229,8 @@
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4154,14 +4247,14 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3" t="s">
-        <v>4</v>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>4</v>
@@ -4178,8 +4271,8 @@
       <c r="AD43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF43" s="3">
         <v>0</v>
@@ -4202,8 +4295,11 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,8 +4408,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4344,35 +4443,35 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>100</v>
       </c>
       <c r="S45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
         <v>200</v>
       </c>
       <c r="U45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W45" s="3">
         <v>100</v>
@@ -4381,10 +4480,10 @@
         <v>100</v>
       </c>
       <c r="Y45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
         <v>100</v>
@@ -4393,10 +4492,10 @@
         <v>100</v>
       </c>
       <c r="AC45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE45" s="3">
         <v>100</v>
@@ -4405,14 +4504,14 @@
         <v>100</v>
       </c>
       <c r="AG45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3">
         <v>100</v>
       </c>
-      <c r="AI45" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
@@ -4422,79 +4521,82 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>11100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>100</v>
-      </c>
-      <c r="W46" s="3">
-        <v>200</v>
       </c>
       <c r="X46" s="3">
         <v>200</v>
       </c>
       <c r="Y46" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z46" s="3">
         <v>400</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>100</v>
       </c>
       <c r="AA46" s="3">
         <v>100</v>
@@ -4503,37 +4605,40 @@
         <v>100</v>
       </c>
       <c r="AC46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD46" s="3">
         <v>400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4564,8 +4669,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4591,8 +4696,8 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>4</v>
+      <c r="V47" s="3">
+        <v>0</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>4</v>
@@ -4609,8 +4714,8 @@
       <c r="AA47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -4642,25 +4747,28 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
         <v>300</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
+      <c r="E48" s="3">
+        <v>300</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G48" s="3">
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
         <v>100</v>
@@ -4672,7 +4780,7 @@
         <v>100</v>
       </c>
       <c r="L48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M48" s="3">
         <v>200</v>
@@ -4687,7 +4795,7 @@
         <v>200</v>
       </c>
       <c r="Q48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -4752,8 +4860,11 @@
       <c r="AL48" s="3">
         <v>0</v>
       </c>
+      <c r="AM48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5132,15 +5252,15 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T52" s="3">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
@@ -5156,8 +5276,8 @@
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
@@ -5168,32 +5288,35 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG52" s="3">
         <v>2600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3900</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>100</v>
       </c>
       <c r="AI52" s="3">
         <v>100</v>
       </c>
       <c r="AJ52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AK52" s="3">
         <v>200</v>
       </c>
       <c r="AL52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AM52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,79 +5425,82 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>100</v>
-      </c>
-      <c r="W54" s="3">
-        <v>200</v>
       </c>
       <c r="X54" s="3">
         <v>200</v>
       </c>
       <c r="Y54" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z54" s="3">
         <v>400</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>100</v>
       </c>
       <c r="AA54" s="3">
         <v>100</v>
@@ -5383,37 +5509,40 @@
         <v>100</v>
       </c>
       <c r="AC54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD54" s="3">
         <v>400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1200</v>
-      </c>
-      <c r="AK54" s="3">
-        <v>700</v>
       </c>
       <c r="AL54" s="3">
         <v>700</v>
       </c>
+      <c r="AM54" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,448 +5622,461 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E57" s="3">
         <v>700</v>
       </c>
       <c r="F57" s="3">
+        <v>700</v>
+      </c>
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>700</v>
       </c>
       <c r="R57" s="3">
         <v>700</v>
       </c>
       <c r="S57" s="3">
+        <v>700</v>
+      </c>
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>800</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>400</v>
       </c>
       <c r="AD57" s="3">
         <v>400</v>
       </c>
       <c r="AE57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF57" s="3">
         <v>500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>600</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>800</v>
       </c>
       <c r="AJ57" s="3">
         <v>800</v>
       </c>
       <c r="AK57" s="3">
+        <v>800</v>
+      </c>
+      <c r="AL57" s="3">
         <v>700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1500</v>
       </c>
       <c r="K58" s="3">
         <v>1500</v>
       </c>
       <c r="L58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M58" s="3">
         <v>900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>800</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>200</v>
       </c>
       <c r="R58" s="3">
         <v>200</v>
       </c>
       <c r="S58" s="3">
+        <v>200</v>
+      </c>
+      <c r="T58" s="3">
         <v>300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5300</v>
-      </c>
-      <c r="W58" s="3">
-        <v>5200</v>
       </c>
       <c r="X58" s="3">
         <v>5200</v>
       </c>
       <c r="Y58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="Z58" s="3">
         <v>5300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>19700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>18600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>18300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>16400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>17000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>7500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
         <v>0</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G59" s="3">
         <v>0</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
+      <c r="H59" s="3">
+        <v>0</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1300</v>
       </c>
       <c r="N59" s="3">
         <v>1300</v>
       </c>
       <c r="O59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P59" s="3">
         <v>1700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>24800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>22700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>21900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>19600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>18800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>11200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5941,11 +6084,11 @@
         <v>300</v>
       </c>
       <c r="E61" s="3">
+        <v>300</v>
+      </c>
+      <c r="F61" s="3">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -5959,13 +6102,13 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>100</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -5983,7 +6126,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>100</v>
@@ -5998,7 +6141,7 @@
         <v>100</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
@@ -6022,28 +6165,31 @@
         <v>0</v>
       </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>16500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>12100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>14200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>14100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6074,21 +6220,21 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>100</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
       </c>
       <c r="O62" s="3">
+        <v>100</v>
+      </c>
+      <c r="P62" s="3">
         <v>200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6101,14 +6247,14 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
+      <c r="V62" s="3">
+        <v>0</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>24800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>22700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>21900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>22300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>19500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>16800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>16600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>14400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-142800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-141200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-137000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-135400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-133100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-124900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-123600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-121700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-119800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-117800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-115800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-113200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-112300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-110300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-108200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-104700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-103100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-101300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-99100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-97200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-93700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-92500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-90000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-85800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-81500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-78400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-75400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-71200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-67700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-63800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-59900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-57100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-55600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-53800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-2100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-2300</v>
       </c>
       <c r="H76" s="3">
         <v>-2300</v>
       </c>
       <c r="I76" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J76" s="3">
         <v>-2200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-3100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1700</v>
       </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
       <c r="N76" s="3">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3">
         <v>1500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-11400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-11300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-11100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-10000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-10900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-24700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-22300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-21600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-18800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-19600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-16300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-18000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-16600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-15300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-13600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-3100</v>
       </c>
       <c r="AC81" s="3">
         <v>-3100</v>
       </c>
       <c r="AD81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,20 +8195,21 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>4</v>
       </c>
@@ -8029,8 +8228,8 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8839,8 +9060,8 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8917,8 +9138,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,8 +9364,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9169,8 +9399,8 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -9247,8 +9477,11 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,118 +9970,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-200</v>
       </c>
       <c r="O100" s="3">
         <v>-200</v>
       </c>
       <c r="P100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>1700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>12700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>500</v>
-      </c>
-      <c r="W100" s="3">
-        <v>400</v>
       </c>
       <c r="X100" s="3">
         <v>400</v>
       </c>
       <c r="Y100" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z100" s="3">
         <v>1000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,114 +10196,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-100</v>
       </c>
       <c r="H102" s="3">
         <v>-100</v>
       </c>
       <c r="I102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-1600</v>
       </c>
       <c r="M102" s="3">
         <v>-1600</v>
       </c>
       <c r="N102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="O102" s="3">
         <v>-1700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>10700</v>
-      </c>
-      <c r="T102" s="3">
-        <v>100</v>
       </c>
       <c r="U102" s="3">
         <v>100</v>
       </c>
       <c r="V102" s="3">
+        <v>100</v>
+      </c>
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>300</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>600</v>
       </c>
     </row>
